--- a/activities/lab-16-operate-a-governed-copilot-pipeline/Lumina-Living-Lab-16.xlsx
+++ b/activities/lab-16-operate-a-governed-copilot-pipeline/Lumina-Living-Lab-16.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Prompt_Log" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Evidence_Register" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Acceptance_Check" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Pilot_Cases" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Pipeline_Control" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Approval_Log" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Pilot_Metrics" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Connected_Workflow" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Scenario" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Prompt_Log" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Evidence_Register" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Acceptance_Check" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Pilot_Cases" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Pipeline_Control" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Approval_Log" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pilot_Metrics" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Acceptance_Check!$A$1:$D$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Approval_Log!$A$1:$E$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Evidence_Register!$A$1:$G$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Pilot_Cases!$A$1:$I$6</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Pilot_Metrics!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Pipeline_Control!$A$1:$G$1</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prompt_Log!$A$1:$F$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Scenario!$A$1:$H$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Acceptance_Check!$A$1:$D$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Approval_Log!$A$1:$E$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Evidence_Register!$A$1:$G$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Pilot_Cases!$A$1:$I$6</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">Pilot_Metrics!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Pipeline_Control!$A$1:$G$1</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Prompt_Log!$A$1:$F$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Scenario!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -37,7 +38,70 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="111">
+  <si>
+    <t xml:space="preserve">Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina Living Pte Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW-2026 Sustainable Workspace Launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-department capstone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina-HR-Policy.docx; Lumina-Analysis.xlsx; Lumina-Management-Report.docx; Lumina-Decision-Deck.pptx; Lumina-Loop-Tasks.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina-Release-Evidence.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete the handoff: review Word and Excel, approve the deck, save the Outlook draft, post a reviewed update in the training Teams channel, and monitor the same Loop actions. Record actual links, recipients, approvals and outcomes; do not mark unperformed actions complete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You work for Lumina Living Pte Ltd on SW-2026, the Sustainable Workspace Launch. HR, Marketing, Finance and Operations share one evidence trail. Launch is planned for 1 October 2026; budget SGD 18,000; target 120 qualified enquiries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumina-HR-Policy.docx; Lumina-Analysis.xlsx; Lumina-Management-Report.docx; Lumina-Decision-Deck.pptx; Lumina-Loop-Tasks.csv. Use your own reviewed prior-lab files first; scenario/ contains supplied fallback examples.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save Lumina-Release-Evidence.xlsx. Record source version, verified facts, unresolved questions and reviewer in Lumina-Living-Lab-16.xlsx. Keep projectSW-2026 and action IDsA01–A04 unchanged. Label every output Draft until reviewed; record actual app actions separately.</t>
+  </si>
   <si>
     <t xml:space="preserve">Lab 16: Operate a Governed End-to-End Copilot Pipeline</t>
   </si>
@@ -63,9 +127,6 @@
     <t xml:space="preserve">Microsoft 365 Copilot agents + Outlook + Teams + Excel</t>
   </si>
   <si>
-    <t xml:space="preserve">Goal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Operate the complete intake-to-delivery pipeline with approvals, exception handling, monitoring and staff handover.</t>
   </si>
   <si>
@@ -81,9 +142,6 @@
     <t xml:space="preserve">K1-K4 · A1-A4</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Learner starter</t>
   </si>
   <si>
@@ -108,7 +166,10 @@
     <t xml:space="preserve">Operate a Governed End-to-End Copilot Pipeline</t>
   </si>
   <si>
-    <t xml:space="preserve">Operate the Lumina Living campaign pipeline on the attached pilot cases. Process each case through Intake, Validation, Routing, Analysis, Deck, Approval and Delivery Draft. At every stage record status, owner, timestamp, evidence and exception. Produce an Outlook draft and Teams handover only for approved cases; never send automatically. Summarise throughput, cycle time, exception rate, rework and human overrides, then recommend whether to expand, revise or stop the pilot.</t>
+    <t xml:space="preserve">Goal: Complete the handoff: review Word and Excel, approve the deck, save the Outlook draft, post a reviewed update in the training Teams channel, and monitor the same Loop actions. Record actual links, recipients, approvals and outcomes; do not mark unperformed actions complete.
+Context: You work for Lumina Living Pte Ltd on SW-2026, the Sustainable Workspace Launch. HR, Marketing, Finance and Operations share one evidence trail. Launch is planned for 1 October 2026; budget SGD 18,000; target 120 qualified enquiries.
+Source: Lumina-HR-Policy.docx; Lumina-Analysis.xlsx; Lumina-Management-Report.docx; Lumina-Decision-Deck.pptx; Lumina-Loop-Tasks.csv. Use your own reviewed prior-lab files first; scenario/ contains supplied fallback examples.
+Expectations: Save Lumina-Release-Evidence.xlsx. Record source version, verified facts, unresolved questions and reviewer in Lumina-Living-Lab-16.xlsx. Keep projectSW-2026 and action IDsA01–A04 unchanged. Label every output Draft until reviewed; record actual app actions separately.</t>
   </si>
   <si>
     <t xml:space="preserve">Attached lab files only</t>
@@ -117,16 +178,10 @@
     <t xml:space="preserve">Learner</t>
   </si>
   <si>
-    <t xml:space="preserve">Not started</t>
-  </si>
-  <si>
     <t xml:space="preserve">Evidence_ID</t>
   </si>
   <si>
     <t xml:space="preserve">Artifact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
   </si>
   <si>
     <t xml:space="preserve">Check</t>
@@ -329,7 +384,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,6 +406,20 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -453,16 +522,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -470,19 +551,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -494,7 +575,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -885,144 +966,255 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="3" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="B10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H10"/>
@@ -1041,7 +1233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1049,51 +1241,51 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="3" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>26</v>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1120,94 +1312,94 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="7"/>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
@@ -1225,7 +1417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1233,38 +1425,38 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1280,7 +1472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1288,186 +1480,186 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="3" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="23"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="9" t="n">
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="12" t="n">
         <v>46300</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="10" t="n">
+      <c r="F2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="13" t="n">
         <v>46286</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="F3" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>46329</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>46329</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7" t="s">
+      <c r="C6" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="E6" s="13" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="G6" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="H6" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>82</v>
+      <c r="I6" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1486,7 +1678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1494,31 +1686,31 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>75</v>
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1542,26 +1734,26 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>87</v>
+    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1577,7 +1769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1585,59 +1777,59 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="3" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" s="6" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="n">
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="n">
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E4"/>
